--- a/laufgruppe.xlsx
+++ b/laufgruppe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukas\Desktop\Floorball\25-26\U13 II\Laufgruppe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B27E25-B0DA-4DA1-9795-D2914803742D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E692A122-909B-4DDC-8BE0-01F61409324A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Läufer" sheetId="1" r:id="rId1"/>
@@ -680,6 +680,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -919,6 +920,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/laufgruppe.xlsx
+++ b/laufgruppe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukas\Desktop\Floorball\25-26\U13 II\Laufgruppe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38F3341-4F57-4C27-9734-965819C4890C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D285F864-EAD2-4CE4-B63F-EDAFF0665182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Läufer" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -32,15 +32,6 @@
     <t>Anmerkung</t>
   </si>
   <si>
-    <t>Niklas</t>
-  </si>
-  <si>
-    <t>Mareike</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
     <t>06.01.2025</t>
   </si>
   <si>
@@ -50,24 +41,6 @@
     <t>20.01.2025</t>
   </si>
   <si>
-    <t>28:10</t>
-  </si>
-  <si>
-    <t>25:30</t>
-  </si>
-  <si>
-    <t>24:00</t>
-  </si>
-  <si>
-    <t>25:00</t>
-  </si>
-  <si>
-    <t>30:05</t>
-  </si>
-  <si>
-    <t>26:00</t>
-  </si>
-  <si>
     <t>ℹ️ Zeit eingeben als: 25:34  (Minuten:Sekunden)</t>
   </si>
   <si>
@@ -75,6 +48,39 @@
   </si>
   <si>
     <t>27.01.2025</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Noah</t>
+  </si>
+  <si>
+    <t>40:25</t>
+  </si>
+  <si>
+    <t>41:26</t>
+  </si>
+  <si>
+    <t>43:20</t>
+  </si>
+  <si>
+    <t>36:00</t>
+  </si>
+  <si>
+    <t>37:00</t>
+  </si>
+  <si>
+    <t>35:25</t>
+  </si>
+  <si>
+    <t>39:18</t>
+  </si>
+  <si>
+    <t>36:20</t>
   </si>
 </sst>
 </file>
@@ -511,35 +517,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>2014</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2">
         <v>2014</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
         <v>2013</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -562,60 +568,62 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/laufgruppe.xlsx
+++ b/laufgruppe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukas\Desktop\Floorball\25-26\U13 II\Laufgruppe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D285F864-EAD2-4CE4-B63F-EDAFF0665182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B2A8D8-729C-48D4-9C68-C24193E8FD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Läufer" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Name</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>36:20</t>
+  </si>
+  <si>
+    <t>Erika</t>
   </si>
 </sst>
 </file>
@@ -539,7 +542,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2">
         <v>2013</v>
@@ -611,7 +614,7 @@
     </row>
     <row r="4" spans="1:5" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>12</v>
